--- a/laporan_padel_dki_jakarta_2026-10-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-19.xlsx
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.495.000</t>
+          <t>Rp3.885.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp752.000</t>
+          <t>Rp1.148.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.030.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp53.000</t>
+          <t>Rp159.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp21.800.000</t>
+          <t>Rp23.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.520.000</t>
+          <t>Rp9.910.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.424.996</t>
+          <t>Rp2.549.996</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp17.970.000</t>
+          <t>Rp18.370.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-19.xlsx
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.005.000</t>
+          <t>Rp805.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp448.000</t>
+          <t>Rp697.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>102</v>
       </c>
       <c r="D70" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.982.000</t>
+          <t>Rp3.783.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.340.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.790.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp159.000</t>
+          <t>Rp301.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.055.000</t>
+          <t>Rp2.235.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.972.000</t>
+          <t>Rp10.632.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.530.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp7.955.000</t>
+          <t>Rp8.065.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp34.700.000</t>
+          <t>Rp34.100.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.180.000</t>
+          <t>Rp5.560.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.745.000</t>
+          <t>Rp3.985.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.549.996</t>
+          <t>Rp2.674.996</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.710.000</t>
+          <t>Rp4.825.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.490.000</t>
+          <t>Rp2.670.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>144</v>
       </c>
       <c r="D35" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.638.000</t>
+          <t>Rp3.737.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.535.000</t>
+          <t>Rp3.235.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-19.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.280.000</t>
+          <t>Rp3.760.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.483.988</t>
+          <t>Rp4.445.990</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.917.000</t>
+          <t>Rp6.267.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp805.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp564.000</t>
+          <t>Rp689.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.979.000</t>
+          <t>Rp3.189.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.885.000</t>
+          <t>Rp3.385.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.290.000</t>
+          <t>Rp10.040.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.620.000</t>
+          <t>Rp2.630.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.972.000</t>
+          <t>Rp4.071.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp4.310.000</t>
+          <t>Rp5.210.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.783.000</t>
+          <t>Rp3.385.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp440.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.252.500</t>
+          <t>Rp11.897.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.844.000</t>
+          <t>Rp2.742.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.325.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.542.000</t>
+          <t>Rp3.238.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.350.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp301.000</t>
+          <t>Rp248.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp860.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp2.673.000</t>
+          <t>Rp4.158.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>92</v>
       </c>
       <c r="D68" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.690.000</t>
+          <t>Rp9.040.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp23.200.000</t>
+          <t>Rp23.700.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp69.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.494.000</t>
+          <t>Rp7.144.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.632.000</t>
+          <t>Rp11.752.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.162.000</t>
+          <t>Rp6.441.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.275.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.950.000</t>
+          <t>Rp9.100.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.876.000</t>
+          <t>Rp3.426.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.574.000</t>
+          <t>Rp2.673.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.900.000</t>
+          <t>Rp20.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.491.000</t>
+          <t>Rp4.016.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp11.625.000</t>
+          <t>Rp11.225.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp18.000.000</t>
+          <t>Rp18.600.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp8.350.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp8.550.000</t>
+          <t>Rp9.380.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.805.000</t>
+          <t>Rp2.705.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.674.996</t>
+          <t>Rp2.799.996</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp18.370.000</t>
+          <t>Rp18.010.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.424.996</t>
+          <t>Rp2.549.996</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.180.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.734.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.235.000</t>
+          <t>Rp3.335.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp820.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp200.000</t>
+          <t>Rp85.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -544,16 +544,16 @@
         <v>184</v>
       </c>
       <c r="D4" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.880.000</t>
+          <t>Rp11.240.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp945.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.445.990</t>
+          <t>Rp4.096.991</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.267.000</t>
+          <t>Rp7.170.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp864.000</t>
+          <t>Rp1.024.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.580.000</t>
+          <t>Rp2.790.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp555.000</t>
+          <t>Rp430.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.189.000</t>
+          <t>Rp3.329.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp3.045.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.184.000</t>
+          <t>Rp1.716.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.170.000</t>
+          <t>Rp5.360.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.385.000</t>
+          <t>Rp2.995.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp4.608.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.620.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp120.000</t>
+          <t>Rp180.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp825.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp3.131.000</t>
+          <t>Rp4.727.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.148.000</t>
+          <t>Rp1.247.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.071.000</t>
+          <t>Rp4.369.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp5.210.000</t>
+          <t>Rp4.985.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp5.421.000</t>
+          <t>Rp5.919.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.340.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>54</v>
       </c>
       <c r="D99" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3535,6 +3535,37 @@
       <c r="G100" t="inlineStr">
         <is>
           <t>Rp165.000 - Rp400.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Playfieldcourt Padel Srengseng</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>14</v>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rp800.000</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -3602,16 +3633,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp162.000</t>
+          <t>Rp324.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3630,19 +3661,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D3" t="n">
         <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.897.500</t>
+          <t>Rp11.844.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3695,16 +3726,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3757,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3912,16 +3943,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.290.000</t>
+          <t>Rp4.080.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4191,16 +4222,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.742.000</t>
+          <t>Rp3.091.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4408,16 +4439,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp8.030.000</t>
+          <t>Rp8.205.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4563,16 +4594,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4718,16 +4749,16 @@
         <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4749,16 +4780,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4949,7 +4980,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp185.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5059,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.992.000</t>
+          <t>Rp2.656.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5059,16 +5090,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.325.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5090,16 +5121,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5245,16 +5276,16 @@
         <v>38</v>
       </c>
       <c r="D55" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp5.885.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5307,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5307,16 +5338,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp248.000</t>
+          <t>Rp452.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5555,16 +5586,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5586,16 +5617,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.158.000</t>
+          <t>Rp5.049.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5617,16 +5648,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.464.000</t>
+          <t>Rp1.684.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5679,16 +5710,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5772,16 +5803,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5803,16 +5834,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp10.800.000</t>
+          <t>Rp11.800.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5885,16 +5916,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5916,16 +5947,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.605.000</t>
+          <t>Rp12.925.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5978,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5978,16 +6009,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6102,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp23.700.000</t>
+          <t>Rp27.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6102,16 +6133,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6164,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6319,16 +6350,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6525,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp8.780.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6556,16 +6587,16 @@
         <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6587,16 +6618,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.370.000</t>
+          <t>Rp9.570.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6618,16 +6649,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp69.000</t>
+          <t>Rp268.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6649,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.910.000</t>
+          <t>Rp10.355.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6742,16 +6773,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.144.000</t>
+          <t>Rp7.616.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6990,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.426.000</t>
+          <t>Rp4.526.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7021,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7083,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7176,21 +7207,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.016.000</t>
+          <t>Rp4.191.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7269,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.530.000</t>
+          <t>Rp4.280.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7362,16 +7393,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7393,16 +7424,16 @@
         <v>84</v>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.290.000</t>
+          <t>Rp4.510.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7455,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7548,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp11.225.000</t>
+          <t>Rp12.700.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7610,16 +7641,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7641,16 +7672,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7734,16 +7765,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp18.600.000</t>
+          <t>Rp19.300.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7765,16 +7796,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp9.950.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7796,16 +7827,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7858,16 +7889,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp8.065.000</t>
+          <t>Rp8.595.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7889,16 +7920,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp34.100.000</t>
+          <t>Rp36.100.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7920,16 +7951,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7982,16 +8013,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp29.700.000</t>
+          <t>Rp19.800.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8044,16 +8075,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp9.380.000</t>
+          <t>Rp8.360.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8075,16 +8106,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8219,16 +8250,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.705.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8250,16 +8281,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.714.000</t>
+          <t>Rp2.234.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8281,16 +8312,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8312,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.794.000</t>
+          <t>Rp2.392.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8374,16 +8405,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp670.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8405,16 +8436,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp260.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8467,16 +8498,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.985.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8529,16 +8560,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8560,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.799.996</t>
+          <t>Rp3.199.994</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8591,16 +8622,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8684,16 +8715,16 @@
         <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8746,16 +8777,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp18.010.000</t>
+          <t>Rp19.930.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8777,16 +8808,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp660.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8808,16 +8839,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.115.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8839,16 +8870,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.670.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8870,16 +8901,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp405.000</t>
+          <t>Rp604.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8963,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9025,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9149,16 +9180,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp590.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9211,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.390.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9211,16 +9242,16 @@
         <v>144</v>
       </c>
       <c r="D35" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.737.000</t>
+          <t>Rp3.837.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9273,16 +9304,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.734.000</t>
+          <t>Rp1.932.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9304,16 +9335,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.335.000</t>
+          <t>Rp4.685.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9335,16 +9366,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp338.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9397,16 +9428,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp120.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,7 +620,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp99.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.096.991</t>
+          <t>Rp4.346.991</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.255.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.240.000</t>
+          <t>Rp1.315.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.369.000</t>
+          <t>Rp4.468.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3296,28 +3296,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Golcindo Padel Club</t>
+          <t>Golcindo Padel &amp; Mahjong</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rp59.000 - Rp149.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
     </row>
@@ -3327,28 +3327,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mono House</t>
+          <t>Golcindo Padel Club</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D94" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp59.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -3358,28 +3358,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Elite Padel Club - Puri</t>
+          <t>Mono House</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp5.919.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp249.000</t>
+          <t>Rp125.000</t>
         </is>
       </c>
     </row>
@@ -3389,28 +3389,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Seven Stars Arena</t>
+          <t>Elite Padel Club - Puri</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp5.919.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp220.000</t>
+          <t>Rp149.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -3420,28 +3420,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deuce Arena</t>
+          <t>Seven Stars Arena</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp250.000</t>
+          <t>Rp75.000 - Rp220.000</t>
         </is>
       </c>
     </row>
@@ -3451,28 +3451,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alley Social Padel Mahjong By Homeground</t>
+          <t>Deuce Arena</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp225.000</t>
+          <t>Rp80.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -3482,28 +3482,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Athena Arena</t>
+          <t>Alley Social Padel Mahjong By Homeground</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp2.575.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp50.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3513,28 +3513,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SERA COMMUNITY CLUB</t>
+          <t>Athena Arena</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D100" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rp1.460.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rp165.000 - Rp400.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -3544,26 +3544,57 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>SERA COMMUNITY CLUB</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>28</v>
+      </c>
+      <c r="D101" t="n">
+        <v>22</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rp1.460.000</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Rp165.000 - Rp400.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>Playfieldcourt Padel Srengseng</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C102" t="n">
         <v>14</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D102" t="n">
         <v>10</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Rp800.000</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Rp150.000 - Rp200.000</t>
         </is>
@@ -4067,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5648,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.684.000</t>
+          <t>Rp1.860.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6009,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6288,16 +6319,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6587,16 +6618,16 @@
         <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6680,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.355.000</t>
+          <t>Rp10.535.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7145,16 +7176,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.500.000</t>
+          <t>Rp20.700.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7207,16 +7238,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.191.000</t>
+          <t>Rp4.201.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7269,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.430.000</t>
+          <t>Rp6.030.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7579,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp12.700.000</t>
+          <t>Rp12.800.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7610,16 +7641,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.360.000</t>
+          <t>Rp5.736.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7641,16 +7672,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.909.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7765,16 +7796,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp19.300.000</t>
+          <t>Rp19.525.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8106,16 +8137,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp6.525.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8250,16 +8281,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.820.000</t>
+          <t>Rp4.945.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8777,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp19.930.000</t>
+          <t>Rp20.530.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
